--- a/diamond_redact_app/templates/PureCarbon_Quote_Template_Natural.xlsx
+++ b/diamond_redact_app/templates/PureCarbon_Quote_Template_Natural.xlsx
@@ -477,13 +477,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Quote Price</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -585,16 +585,6 @@
       <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Ratio</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
         </is>
       </c>
     </row>
@@ -665,12 +655,6 @@
       </c>
       <c r="Q2" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -691,8 +675,6 @@
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
@@ -712,8 +694,6 @@
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
@@ -733,8 +713,6 @@
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n"/>
@@ -754,8 +732,6 @@
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -775,8 +751,6 @@
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -856,7 +830,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Price is optional — fill it in only if you want a price to show on the quote. Leave it blank and no price appears.</t>
+          <t>Quote Price is optional — fill it in only if you want a price to show on the quote. Leave it blank and no price appears.</t>
         </is>
       </c>
     </row>
